--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2020_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2020_aysen.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:34</t>
+    <t xml:space="preserve">2026-09-09 20:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2020_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2020_aysen.xlsx
@@ -24,36 +24,36 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Coyhaique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lago Verde</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aysén</t>
   </si>
   <si>
+    <t xml:space="preserve">Cisnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guaitecas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cochrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O Higgins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tortel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chile Chico</t>
   </si>
   <si>
-    <t xml:space="preserve">Cisnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cochrane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guaitecas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lago Verde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O Higgins</t>
-  </si>
-  <si>
     <t xml:space="preserve">Río Ibáñez</t>
   </si>
   <si>
-    <t xml:space="preserve">Tortel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:36</t>
+    <t xml:space="preserve">2026-09-18 10:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -475,7 +475,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7.43</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="3">
@@ -483,7 +483,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7.04</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5.99</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.79</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6.63</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3.41</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="8">
@@ -523,7 +523,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6.61</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.46</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="10">
@@ -539,7 +539,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.08</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="11">
@@ -547,7 +547,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2.17</v>
+        <v>5.08</v>
       </c>
     </row>
   </sheetData>
